--- a/plc/s7-1x00/core/adt/stack/EStackStatus-v1.0.xlsx
+++ b/plc/s7-1x00/core/adt/stack/EStackStatus-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\adt\stack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CABC83-1F4B-45CE-A37C-D2A6FF485722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C48F39-FF86-4F27-952D-A89548ED08A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,10 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/stack"}</t>
-  </si>
-  <si>
     <t>EStackStatus</t>
+  </si>
+  <si>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/stack","status": "current", "deprecatedBy": null, "dependencies"  : []}</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
@@ -548,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
